--- a/docs/package/05_Delivery/Upload_Templates/Leads_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Leads_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="122">
   <si>
     <t xml:space="preserve">First Name</t>
   </si>
@@ -39,22 +39,28 @@
     <t xml:space="preserve">Contact Number</t>
   </si>
   <si>
-    <t xml:space="preserve">House No</t>
+    <t xml:space="preserve">House / Unit No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Street</t>
   </si>
   <si>
     <t xml:space="preserve">Barangay</t>
   </si>
   <si>
-    <t xml:space="preserve">City</t>
+    <t xml:space="preserve">City / Municipality</t>
   </si>
   <si>
     <t xml:space="preserve">Province</t>
   </si>
   <si>
+    <t xml:space="preserve">Region</t>
+  </si>
+  <si>
     <t xml:space="preserve">Country</t>
   </si>
   <si>
-    <t xml:space="preserve">Zip Code</t>
+    <t xml:space="preserve">ZIP Code</t>
   </si>
   <si>
     <t xml:space="preserve">Lead Category</t>
@@ -222,25 +228,46 @@
     <t xml:space="preserve">contactNumber, mobile, mobilenumber, phone</t>
   </si>
   <si>
-    <t xml:space="preserve">House number and street</t>
-  </si>
-  <si>
-    <t xml:space="preserve">houseNo, address, street</t>
+    <t xml:space="preserve">House, unit, floor and building</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit 1203, Tower 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">houseNo, house no, address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Street, subdivision or village</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mabini St.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">street, road, street name</t>
   </si>
   <si>
     <t xml:space="preserve">barangay, district, subdivision</t>
   </si>
   <si>
-    <t xml:space="preserve">City or municipality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">city</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Province or region</t>
+    <t xml:space="preserve">City or municipality of the City / Municipality master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">city, municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province of the Province master (Metro Manila for NCR)</t>
   </si>
   <si>
     <t xml:space="preserve">province, state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region of the Region master (filled from the province when empty)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Capital Region (NCR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">region</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
@@ -480,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -491,19 +518,21 @@
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="12" max="12" width="25" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="19" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="17" max="17" width="19" customWidth="1"/>
     <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="20" customHeight="1">
+    <row r="1" spans="1:20" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -558,42 +587,42 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="0" t="s">
         <v>29</v>
       </c>
       <c r="O2" s="0" t="s">
@@ -608,37 +637,37 @@
       <c r="R2" s="0" t="s">
         <v>33</v>
       </c>
+      <c r="S2" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="T2" s="0" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="3">
       <c r="D3" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O3" s="0" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="P3" s="0" t="s">
         <v>43</v>
@@ -648,6 +677,12 @@
       </c>
       <c r="R3" s="0" t="s">
         <v>45</v>
+      </c>
+      <c r="S3" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="T3" s="0" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -657,7 +692,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -670,22 +705,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
@@ -693,16 +728,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -710,16 +745,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="E3" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
@@ -727,16 +762,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -744,13 +779,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -758,16 +793,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -775,19 +810,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">
@@ -795,16 +830,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
@@ -812,16 +847,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -829,16 +864,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -846,16 +881,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12">
@@ -863,16 +898,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -880,16 +915,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14">
@@ -897,16 +932,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -914,16 +949,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16">
@@ -931,19 +966,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>30</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17">
@@ -951,16 +983,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E17" s="0" t="s">
         <v>31</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -968,19 +1000,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E18" s="0" t="s">
         <v>32</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
@@ -988,16 +1020,53 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1016,106 +1085,106 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/docs/package/05_Delivery/Upload_Templates/Leads_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Leads_Upload_Template.xlsx
@@ -300,10 +300,10 @@
     <t xml:space="preserve">lob, line of business, product</t>
   </si>
   <si>
-    <t xml:space="preserve">Text; bulk-upload when empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">source</t>
+    <t xml:space="preserve">Lead source of Master &gt; Insurance Management &gt; Lead Sources (code or name); bulk-upload when empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source, lead source</t>
   </si>
   <si>
     <t xml:space="preserve">Item</t>
@@ -388,7 +388,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -415,8 +415,42 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5F6B76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -444,6 +478,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -475,9 +527,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -498,6 +550,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/docs/package/05_Delivery/Upload_Templates/Leads_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Leads_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="125">
   <si>
     <t xml:space="preserve">First Name</t>
   </si>
@@ -72,6 +72,9 @@
     <t xml:space="preserve">LOB</t>
   </si>
   <si>
+    <t xml:space="preserve">Product</t>
+  </si>
+  <si>
     <t xml:space="preserve">Source</t>
   </si>
   <si>
@@ -291,13 +294,19 @@
     <t xml:space="preserve">taxInformationNumber, tax number</t>
   </si>
   <si>
-    <t xml:space="preserve">Line of business</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOTOR, FIRE, IAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lob, line of business, product</t>
+    <t xml:space="preserve">Line of business (Line of Business master code or name); empty: the product is tagged later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lob, line of business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active product of Master &gt; Product (code or name) of the LOB; empty: the product is tagged later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">product, product code, product name</t>
   </si>
   <si>
     <t xml:space="preserve">Lead source of Master &gt; Insurance Management &gt; Lead Sources (code or name); bulk-upload when empty</t>
@@ -566,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -589,9 +598,10 @@
     <col min="18" max="18" width="14" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="20" customHeight="1">
+    <row r="1" spans="1:21" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -652,96 +662,99 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q2" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R2" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S2" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="T2" s="0" t="s">
         <v>35</v>
+      </c>
+      <c r="U2" s="0" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="D3" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O3" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P3" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q3" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R3" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S3" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="T3" s="0" t="s">
         <v>47</v>
+      </c>
+      <c r="U3" s="0" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -751,7 +764,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -764,22 +777,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2">
@@ -787,16 +800,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -804,16 +817,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -821,16 +834,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -838,13 +851,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
@@ -852,16 +865,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -869,19 +882,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
@@ -889,16 +902,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
@@ -906,16 +919,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -923,16 +936,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
@@ -940,16 +953,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12">
@@ -957,16 +970,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
@@ -974,16 +987,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
@@ -991,16 +1004,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
@@ -1008,16 +1021,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
@@ -1025,16 +1038,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17">
@@ -1042,16 +1055,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18">
@@ -1059,19 +1072,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
@@ -1079,16 +1092,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20">
@@ -1096,16 +1109,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" s="4" t="s">
         <v>93</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>94</v>
@@ -1116,16 +1126,33 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>95</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1144,106 +1171,106 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/docs/package/05_Delivery/Upload_Templates/Leads_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Leads_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="125">
   <si>
     <t xml:space="preserve">First Name</t>
   </si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">009-876-543-000</t>
   </si>
   <si>
-    <t xml:space="preserve">FIRE</t>
+    <t xml:space="preserve">Motor Vehicle Insurance</t>
   </si>
   <si>
     <t xml:space="preserve">Walk-in</t>
@@ -395,7 +395,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -751,6 +751,9 @@
         <v>46</v>
       </c>
       <c r="S3" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" s="0" t="s">
         <v>47</v>
       </c>
       <c r="U3" s="0" t="s">

--- a/docs/package/05_Delivery/Upload_Templates/Leads_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Leads_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="141">
   <si>
     <t xml:space="preserve">First Name</t>
   </si>
@@ -78,6 +78,21 @@
     <t xml:space="preserve">Source</t>
   </si>
   <si>
+    <t xml:space="preserve">Customer Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disposition</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maria</t>
   </si>
   <si>
@@ -315,6 +330,42 @@
     <t xml:space="preserve">source, lead source</t>
   </si>
   <si>
+    <t xml:space="preserve">TFS, Non-TFS or Direct Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFS, Non-TFS, Direct Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">customerType, customer type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFS loan of the prospect; a Loan ID already loaded updates that prospect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loanId, loan number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LD number of a prospect already loaded: the row updates its status and disposition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leadNumber, prospect number, lead no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prospect status: New, Contacted, Qualified, QuoteGenerated, Converted, Lost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status, call status, lead status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interested, Not Interested, Uncontacted, Call back or Renewed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disposition, call disposition</t>
+  </si>
+  <si>
     <t xml:space="preserve">Item</t>
   </si>
   <si>
@@ -333,12 +384,6 @@
     <t xml:space="preserve">Operations &gt; Sales &amp; Marketing &gt; Prospects &gt; Bulk Upload</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/leads/bulk-upload (multipart field "file")</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -348,7 +393,7 @@
     <t xml:space="preserve">Row limit</t>
   </si>
   <si>
-    <t xml:space="preserve">Up to 20,000 data rows per file (IMPORT_MAX_ROWS) and 10 MB (IMPORT_MAX_MB).</t>
+    <t xml:space="preserve">Up to 20,000 data rows per file and 10 MB.</t>
   </si>
   <si>
     <t xml:space="preserve">Required columns</t>
@@ -387,7 +432,10 @@
     <t xml:space="preserve">A lead needs a First Name (individual) or a Company Name (corporate).</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -575,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:Z3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -599,9 +647,14 @@
     <col min="19" max="19" width="14" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
+    <col min="22" max="22" width="19" customWidth="1"/>
+    <col min="23" max="23" width="14" customWidth="1"/>
+    <col min="24" max="24" width="17" customWidth="1"/>
+    <col min="25" max="25" width="14" customWidth="1"/>
+    <col min="26" max="26" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="20" customHeight="1">
+    <row r="1" spans="1:26" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -665,99 +718,114 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="O2" s="0" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="0" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R2" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="S2" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="U2" s="0" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="D3" s="0" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I3" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q3" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="R3" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="S3" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="O3" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q3" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="R3" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="S3" s="0" t="s">
-        <v>35</v>
-      </c>
       <c r="T3" s="0" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="U3" s="0" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -767,7 +835,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -780,22 +848,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
@@ -803,16 +871,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
@@ -820,16 +888,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
@@ -837,16 +905,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
@@ -854,13 +922,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -868,16 +936,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -885,19 +953,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
@@ -905,16 +973,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
@@ -922,16 +990,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +1007,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -956,16 +1024,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
@@ -973,16 +1041,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
@@ -990,16 +1058,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
@@ -1007,16 +1075,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15">
@@ -1024,16 +1092,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -1041,16 +1109,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -1058,16 +1126,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18">
@@ -1075,19 +1143,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
@@ -1095,16 +1163,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20">
@@ -1112,16 +1180,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21">
@@ -1129,16 +1197,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22">
@@ -1146,16 +1214,92 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>99</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1165,7 +1309,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1174,106 +1318,98 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/docs/package/05_Delivery/Upload_Templates/Leads_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Leads_Upload_Template.xlsx
@@ -381,7 +381,7 @@
     <t xml:space="preserve">Upload on</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; Sales &amp; Marketing &gt; Prospects &gt; Bulk Upload</t>
+    <t xml:space="preserve">Sales &amp; Placement &gt; Prospects &gt; Bulk Upload</t>
   </si>
   <si>
     <t xml:space="preserve">File types</t>
